--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3087,6 +3087,989 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127919205</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98376</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>516056</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6691410</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127919736</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>515849</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6691351</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127919526</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>516038</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6691399</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127918679</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>515876</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6691607</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127919913</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>515818</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6691334</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127882305</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>515632</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6691364</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127918921</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>515936</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6691502</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127920131</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>515586</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6691323</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127925429</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hopsveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>515784</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6691412</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp på tallstam.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -3092,7 +3092,7 @@
         <v>127919205</v>
       </c>
       <c r="B25" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>127919736</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>127919526</v>
       </c>
       <c r="B27" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127918679</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>127919913</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>127882305</v>
       </c>
       <c r="B30" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>127918921</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127920131</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127925429</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -3092,7 +3092,7 @@
         <v>127919205</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>98387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>127919736</v>
       </c>
       <c r="B26" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>127919526</v>
       </c>
       <c r="B27" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127918679</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>127919913</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>127882305</v>
       </c>
       <c r="B30" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>127918921</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127920131</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127925429</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -3092,7 +3092,7 @@
         <v>127919205</v>
       </c>
       <c r="B25" t="n">
-        <v>98387</v>
+        <v>98388</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>127919736</v>
       </c>
       <c r="B26" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>127919526</v>
       </c>
       <c r="B27" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127918679</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>127919913</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>127882305</v>
       </c>
       <c r="B30" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>127918921</v>
       </c>
       <c r="B31" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127920131</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -3092,7 +3092,7 @@
         <v>127919205</v>
       </c>
       <c r="B25" t="n">
-        <v>98388</v>
+        <v>98389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>127919736</v>
       </c>
       <c r="B26" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>127919526</v>
       </c>
       <c r="B27" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127918679</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>127919913</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>127882305</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>127918921</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127920131</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -3092,7 +3092,7 @@
         <v>127919205</v>
       </c>
       <c r="B25" t="n">
-        <v>98389</v>
+        <v>98390</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>127919736</v>
       </c>
       <c r="B26" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>127919526</v>
       </c>
       <c r="B27" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127918679</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>127919913</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>127882305</v>
       </c>
       <c r="B30" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>127918921</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127920131</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -3092,7 +3092,7 @@
         <v>127919205</v>
       </c>
       <c r="B25" t="n">
-        <v>98390</v>
+        <v>98398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>127919736</v>
       </c>
       <c r="B26" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>127919526</v>
       </c>
       <c r="B27" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127918679</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>127919913</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>127882305</v>
       </c>
       <c r="B30" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>127918921</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127920131</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127925429</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -3092,7 +3092,7 @@
         <v>127919205</v>
       </c>
       <c r="B25" t="n">
-        <v>98398</v>
+        <v>98491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>127919736</v>
       </c>
       <c r="B26" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>127919526</v>
       </c>
       <c r="B27" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127918679</v>
       </c>
       <c r="B28" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>127919913</v>
       </c>
       <c r="B29" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>127882305</v>
       </c>
       <c r="B30" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>127918921</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127920131</v>
       </c>
       <c r="B32" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127925429</v>
       </c>
       <c r="B33" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -3092,7 +3092,7 @@
         <v>127919205</v>
       </c>
       <c r="B25" t="n">
-        <v>98491</v>
+        <v>98505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>127919736</v>
       </c>
       <c r="B26" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>127919526</v>
       </c>
       <c r="B27" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127918679</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>127919913</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>127882305</v>
       </c>
       <c r="B30" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>127918921</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>127920131</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>127925429</v>
       </c>
       <c r="B33" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68048291</v>
+        <v>112980390</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmtjärn Omr. 23 N Bogsnan, Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515874.0181747016</v>
+        <v>515658</v>
       </c>
       <c r="R2" t="n">
-        <v>6691430.073289338</v>
+        <v>6691191</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-10-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,31 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Stig-Åke Svenson, Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
-        </is>
-      </c>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112980390</v>
+        <v>112980570</v>
       </c>
       <c r="B3" t="n">
-        <v>78140</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,14 +805,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515658</v>
+        <v>515734</v>
       </c>
       <c r="R3" t="n">
-        <v>6691191</v>
+        <v>6691192</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -896,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112988395</v>
+        <v>112982756</v>
       </c>
       <c r="B4" t="n">
-        <v>78140</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,17 +903,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedefäbodarna (Hedefäbodarna), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516025</v>
+        <v>515747</v>
       </c>
       <c r="R4" t="n">
-        <v>6691408</v>
+        <v>6691229</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,58 +969,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112983379</v>
+        <v>112983156</v>
       </c>
       <c r="B5" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515737</v>
+        <v>515807</v>
       </c>
       <c r="R5" t="n">
-        <v>6691323</v>
+        <v>6691301</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,54 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112984062</v>
+        <v>112983424</v>
       </c>
       <c r="B6" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515821</v>
+        <v>515717</v>
       </c>
       <c r="R6" t="n">
-        <v>6691393</v>
+        <v>6691347</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112983424</v>
+        <v>112981544</v>
       </c>
       <c r="B7" t="n">
-        <v>78140</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,38 +1176,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515718</v>
+        <v>515601</v>
       </c>
       <c r="R7" t="n">
-        <v>6691347</v>
+        <v>6691316</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,58 +1263,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112983346</v>
+        <v>112983657</v>
       </c>
       <c r="B8" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515737</v>
+        <v>515702</v>
       </c>
       <c r="R8" t="n">
-        <v>6691341</v>
+        <v>6691430</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,54 +1361,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112983969</v>
+        <v>127882305</v>
       </c>
       <c r="B9" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515773</v>
+        <v>515632</v>
       </c>
       <c r="R9" t="n">
-        <v>6691391</v>
+        <v>6691364</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,12 +1426,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,27 +1456,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112982756</v>
+        <v>112980603</v>
       </c>
       <c r="B10" t="n">
-        <v>78140</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,35 +1479,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515746</v>
+        <v>515720</v>
       </c>
       <c r="R10" t="n">
-        <v>6691229</v>
+        <v>6691206</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1625,54 +1570,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112981308</v>
+        <v>112983465</v>
       </c>
       <c r="B11" t="n">
-        <v>97215</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515659</v>
+        <v>515691</v>
       </c>
       <c r="R11" t="n">
-        <v>6691312</v>
+        <v>6691360</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1702,11 +1642,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,58 +1668,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112983599</v>
+        <v>127919736</v>
       </c>
       <c r="B12" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515736</v>
+        <v>515849</v>
       </c>
       <c r="R12" t="n">
-        <v>6691415</v>
+        <v>6691351</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1808,12 +1744,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,76 +1758,68 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112982468</v>
+        <v>112983165</v>
       </c>
       <c r="B13" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515680</v>
+        <v>515807</v>
       </c>
       <c r="R13" t="n">
-        <v>6691368</v>
+        <v>6691301</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,54 +1875,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112983465</v>
+        <v>68048291</v>
       </c>
       <c r="B14" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Holmtjärn Omr. 23 N Bogsnan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515691</v>
+        <v>515874</v>
       </c>
       <c r="R14" t="n">
-        <v>6691360</v>
+        <v>6691430</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2018,12 +1942,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2017-10-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2017-10-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,66 +1972,70 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Anders Bertilsson, Stig-Åke Svenson, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112983156</v>
+        <v>112980501</v>
       </c>
       <c r="B15" t="n">
-        <v>78140</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515807</v>
+        <v>515608</v>
       </c>
       <c r="R15" t="n">
-        <v>6691301</v>
+        <v>6691373</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,15 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112983657</v>
+        <v>127925429</v>
       </c>
       <c r="B16" t="n">
-        <v>90029</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,38 +2102,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Hopsveden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515702</v>
+        <v>515784</v>
       </c>
       <c r="R16" t="n">
-        <v>6691429</v>
+        <v>6691412</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2224,12 +2164,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp på tallstam.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2244,63 +2199,58 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112981544</v>
+        <v>112981580</v>
       </c>
       <c r="B17" t="n">
-        <v>90029</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515601</v>
+        <v>515571</v>
       </c>
       <c r="R17" t="n">
-        <v>6691315</v>
+        <v>6691350</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2362,12 +2312,7 @@
         <v>112981235</v>
       </c>
       <c r="B18" t="n">
-        <v>97215</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2396,14 +2341,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515652</v>
+        <v>515651</v>
       </c>
       <c r="R18" t="n">
-        <v>6691298</v>
+        <v>6691297</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2462,54 +2407,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112983982</v>
+        <v>112981308</v>
       </c>
       <c r="B19" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515781</v>
+        <v>515659</v>
       </c>
       <c r="R19" t="n">
-        <v>6691393</v>
+        <v>6691312</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2539,6 +2479,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-10-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2568,12 +2513,7 @@
         <v>112982615</v>
       </c>
       <c r="B20" t="n">
-        <v>97215</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,7 +2542,7 @@
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2668,59 +2608,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112980501</v>
+        <v>112982468</v>
       </c>
       <c r="B21" t="n">
-        <v>56781</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515608</v>
+        <v>515679</v>
       </c>
       <c r="R21" t="n">
-        <v>6691374</v>
+        <v>6691368</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2776,15 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112983461</v>
+        <v>112983346</v>
       </c>
       <c r="B22" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,21 +2738,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515691</v>
+        <v>515737</v>
       </c>
       <c r="R22" t="n">
-        <v>6691360</v>
+        <v>6691341</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2879,58 +2812,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112980603</v>
+        <v>112983379</v>
       </c>
       <c r="B23" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515720</v>
+        <v>515737</v>
       </c>
       <c r="R23" t="n">
-        <v>6691206</v>
+        <v>6691323</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2986,54 +2914,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112983165</v>
+        <v>112983461</v>
       </c>
       <c r="B24" t="n">
-        <v>89993</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Drättjan (Drättjan), Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515807</v>
+        <v>515691</v>
       </c>
       <c r="R24" t="n">
-        <v>6691301</v>
+        <v>6691360</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3089,56 +3012,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127919205</v>
+        <v>112983599</v>
       </c>
       <c r="B25" t="n">
-        <v>98505</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Drättjan, Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>516056</v>
+        <v>515736</v>
       </c>
       <c r="R25" t="n">
-        <v>6691410</v>
+        <v>6691415</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3162,12 +3082,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,78 +3096,67 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127919736</v>
+        <v>112983969</v>
       </c>
       <c r="B26" t="n">
-        <v>92766</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Drättjan, Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515849</v>
+        <v>515774</v>
       </c>
       <c r="R26" t="n">
-        <v>6691351</v>
+        <v>6691391</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3271,12 +3180,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,70 +3194,67 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127919526</v>
+        <v>112983982</v>
       </c>
       <c r="B27" t="n">
-        <v>91464</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Drättjan, Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>516038</v>
+        <v>515781</v>
       </c>
       <c r="R27" t="n">
-        <v>6691399</v>
+        <v>6691392</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3372,12 +3278,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3386,29 +3292,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127918679</v>
+        <v>112984062</v>
       </c>
       <c r="B28" t="n">
-        <v>98585</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3433,32 +3338,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Drättjan, Dlr</t>
+          <t>Drättjan, Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515876</v>
+        <v>515821</v>
       </c>
       <c r="R28" t="n">
-        <v>6691607</v>
+        <v>6691393</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3482,12 +3376,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3496,29 +3390,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127919913</v>
+        <v>127918679</v>
       </c>
       <c r="B29" t="n">
-        <v>98585</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3545,7 +3438,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3562,10 +3455,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515818</v>
+        <v>515876</v>
       </c>
       <c r="R29" t="n">
-        <v>6691334</v>
+        <v>6691607</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3625,48 +3518,60 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127882305</v>
+        <v>127918921</v>
       </c>
       <c r="B30" t="n">
-        <v>91464</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Drättjan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515632</v>
+        <v>515936</v>
       </c>
       <c r="R30" t="n">
-        <v>6691364</v>
+        <v>6691502</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3693,49 +3598,40 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127918921</v>
+        <v>127919913</v>
       </c>
       <c r="B31" t="n">
-        <v>98585</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3762,7 +3658,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3779,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515936</v>
+        <v>515818</v>
       </c>
       <c r="R31" t="n">
-        <v>6691502</v>
+        <v>6691334</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3845,7 +3741,7 @@
         <v>127920131</v>
       </c>
       <c r="B32" t="n">
-        <v>98585</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3952,10 +3848,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127925429</v>
+        <v>112988395</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>79359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3963,45 +3859,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hopsveden, Dlr</t>
+          <t>Hedefäbodarna, Hedefäbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>515784</v>
+        <v>516025</v>
       </c>
       <c r="R33" t="n">
-        <v>6691412</v>
+        <v>6691408</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4025,27 +3914,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack högt upp på tallstam.</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4060,15 +3934,222 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127919526</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>516038</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6691399</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127919205</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Drättjan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>516056</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6691410</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37473-2025 artfynd.xlsx
+++ b/artfynd/A 37473-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112980390</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112980570</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982756</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983156</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983424</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112988395</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112981544</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983657</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127882305</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,6 +1714,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127919526</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112980603</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983465</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127919736</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2071,6 +2141,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983165</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68048291</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2287,6 +2367,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112980501</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127925429</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2505,6 +2595,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112981580</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2603,6 +2698,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112981235</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2706,6 +2806,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112981308</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2804,6 +2909,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982615</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2906,6 +3016,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112982468</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3008,6 +3123,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983346</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3110,6 +3230,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983379</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3208,6 +3333,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983461</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3310,6 +3440,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983599</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3408,6 +3543,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983969</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3506,6 +3646,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112983982</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3604,6 +3749,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112984062</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3714,6 +3864,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127918679</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3824,6 +3979,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127918921</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3934,6 +4094,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127919913</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4044,6 +4209,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127920131</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4150,8 +4320,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127919205</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>